--- a/data/archive/2026-10-08.xlsx
+++ b/data/archive/2026-10-08.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:47 UTC</t>
+          <t>2026-10-08 17:25 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>Full Stack Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1907,13 +1907,13 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>R0240412</t>
+          <t>R0248060</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:48 UTC</t>
+          <t>2026-10-08 17:27 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Product Engineering Intern</t>
+          <t>C++ Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>Beavercreek, OH</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1985,63 +1985,146 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>R0240412</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 17:27 UTC</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Product Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Product Engineer</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>McLean, VA</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
           <t>R0250655</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08 16:48 UTC</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 17:27 UTC</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q18"/>
+  <autoFilter ref="A1:Q19"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2068,6 +2151,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/archive/2026-10-08.xlsx
+++ b/data/archive/2026-10-08.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Khan Academy</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Cloud Infrastructure</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Remote, USA</t>
+          <t>Remote (US + Canada Only)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -605,22 +605,22 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>8257909</t>
+          <t>8250259</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
+          <t>https://job-boards.greenhouse.io/khanacademy/jobs/8250259</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -667,12 +667,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform Access (L2)</t>
+          <t>Full Stack Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -682,12 +682,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -697,27 +697,23 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>8026211</t>
+          <t>R0248060</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +728,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:13 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -754,22 +750,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (NYC)</t>
+          <t>Data Engineer - Talent Acquisition Operations</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>New York, New York, United States</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -784,27 +780,23 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8008649003</t>
+          <t>1b690123-1766-4e75-a0ef-0f58afa864b4</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
+          <t>https://jobs.lever.co/palantir/1b690123-1766-4e75-a0ef-0f58afa864b4</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +811,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -841,12 +833,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (SF)</t>
+          <t>New Grad Software Engineer, Product Engineering</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -856,12 +848,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -871,17 +863,17 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8010617003</t>
+          <t>8248317</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -891,7 +883,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +898,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -928,12 +920,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer, Infrastructure Platform</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -943,17 +935,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -963,12 +955,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8011590003</t>
+          <t>8859182002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +970,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +985,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1015,27 +1007,27 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
+          <t>Security Engineer Intern [Winter 2027]</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1045,17 +1037,17 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8008645003</t>
+          <t>4719593006</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1057,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4719593006</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1072,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1102,12 +1094,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Backend (Search)</t>
+          <t>Software Engineer, Platform Access (L2)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1117,7 +1109,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1132,17 +1124,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8005406003</t>
+          <t>8026211</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1144,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1159,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1189,12 +1181,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer, Software Updates</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1204,17 +1196,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1229,7 +1221,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8817974002</t>
+          <t>8230855</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1231,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1246,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1276,12 +1268,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure Platform</t>
+          <t>Systems Software Engineer, AI and Cloud - New College Grad 2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1291,12 +1283,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1306,27 +1298,23 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8859182002</t>
+          <t>JR2025458</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Systems-Software-Engineer---AI-and-Cloud---New-College-Grad-2026_JR2025458</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1341,7 +1329,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:11 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1363,27 +1351,27 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer Intern [Winter 2027]</t>
+          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1398,12 +1386,12 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>4719593006</t>
+          <t>8817974002</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1413,7 +1401,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4719593006</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1428,7 +1416,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1450,12 +1438,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Khan Academy</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1465,12 +1453,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Remote (US + Canada Only)</t>
+          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1480,27 +1468,23 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8250259</t>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/khanacademy/jobs/8250259</t>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1515,7 +1499,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1537,12 +1521,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>New Grad Software Engineer, Product Engineering</t>
+          <t>Software Engineer, Early Career (NYC)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1552,12 +1536,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>New York, New York, United States</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1567,7 +1551,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1577,7 +1561,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8248317</t>
+          <t>8008649003</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1587,7 +1571,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1602,7 +1586,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1624,12 +1608,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Updates</t>
+          <t>Software Engineer, Early Career (SF)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1639,12 +1623,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1664,7 +1648,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8230855</t>
+          <t>8010617003</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1674,7 +1658,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1689,7 +1673,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1711,12 +1695,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
+          <t>Software Engineer, Web3 Backend</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1726,38 +1710,42 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
+          <t>Menlo Park, CA; New York, NY</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>8258305</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1772,7 +1760,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1794,12 +1782,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Systems Software Engineer, AI and Cloud - New College Grad 2026</t>
+          <t>Staff Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1809,12 +1797,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1827,20 +1815,24 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>JR2025458</t>
+          <t>8257909</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Systems-Software-Engineer---AI-and-Cloud---New-College-Grad-2026_JR2025458</t>
+          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1855,7 +1847,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:25 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1877,12 +1869,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Junior</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1892,38 +1884,42 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>R0248060</t>
+          <t>8011590003</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1938,7 +1934,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:27 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1960,12 +1956,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1975,38 +1971,42 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>R0240412</t>
+          <t>8008645003</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:27 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2043,88 +2043,258 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Backend (Search)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Remote US</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>8005406003</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 18:09 UTC</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Booz Allen Hamilton</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>C++ Software Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Beavercreek, OH</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>R0240412</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 18:13 UTC</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Product Engineering Intern</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Product Engineer</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>McLean, VA</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>R0250655</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08 17:27 UTC</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 18:13 UTC</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q19"/>
+  <autoFilter ref="A1:Q21"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2152,6 +2322,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
